--- a/Excel/CIRCUITO ISSUNNE/Planilla_Seguimiento_UPCM_ISSUNNE.xlsx
+++ b/Excel/CIRCUITO ISSUNNE/Planilla_Seguimiento_UPCM_ISSUNNE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hernán\Desktop\CIRCUITO ISSUNNE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hernán\Desktop\Administracion HernanMayol\Python_ISSUNNE\Excel\CIRCUITO ISSUNNE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99847F7F-26F2-42F2-96A5-0B4DBABF17B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFB6F35-0B89-48A9-86B6-12C826873641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1036,23 +1036,23 @@
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
       <c r="D3" s="5">
-        <v>46019</v>
+        <v>46133</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="5">
-        <v>46024</v>
+        <v>46133</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="12" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="5">
-        <v>46024</v>
+        <v>46134</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="L3" s="14" t="s">
         <v>14</v>
@@ -1065,7 +1065,7 @@
       )
    )
 )</f>
-        <v>🔴 Pendiente</v>
+        <v>🟠 Pendiente</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -1073,11 +1073,11 @@
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
       <c r="D4" s="7">
-        <v>46047</v>
+        <v>46117</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7">
-        <v>46049</v>
+        <v>46118</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="13" t="s">
@@ -1087,7 +1087,7 @@
       <c r="J4" s="10"/>
       <c r="K4" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="L4" s="14" t="s">
         <v>14</v>
@@ -1100,7 +1100,7 @@
       )
    )
 )</f>
-        <v>🟠 Pendiente</v>
+        <v>🔴 Pendiente</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1169,7 +1169,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>

--- a/Excel/CIRCUITO ISSUNNE/Planilla_Seguimiento_UPCM_ISSUNNE.xlsx
+++ b/Excel/CIRCUITO ISSUNNE/Planilla_Seguimiento_UPCM_ISSUNNE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hernán\Desktop\Administracion HernanMayol\Python_ISSUNNE\Excel\CIRCUITO ISSUNNE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFB6F35-0B89-48A9-86B6-12C826873641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8F17B9-3785-4CC7-879C-FBFE2BE2681B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,6 +240,27 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -578,27 +599,6 @@
         </top>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -613,24 +613,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{327A5397-3B0C-43C9-85BE-3CBA3FCDD768}" name="Tabla1" displayName="Tabla1" ref="A1:M5" totalsRowShown="0" tableBorderDxfId="13">
-  <autoFilter ref="A1:M5" xr:uid="{327A5397-3B0C-43C9-85BE-3CBA3FCDD768}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{327A5397-3B0C-43C9-85BE-3CBA3FCDD768}" name="Tabla1" displayName="Tabla1" ref="A1:M6" totalsRowShown="0" tableBorderDxfId="16">
+  <autoFilter ref="A1:M6" xr:uid="{327A5397-3B0C-43C9-85BE-3CBA3FCDD768}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{48377B2A-C8AB-4075-A29A-A504CD024988}" name="Afiliado" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{FD0798EF-A11B-4C36-990B-871354CA5378}" name="DNI" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{FB341455-6534-4F40-A9B7-3851902BD371}" name="Estudio solicitado" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{2717F401-A0B9-4F33-8834-D45B603910EB}" name="Fecha solicitud" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{C94858FC-A376-4E19-928A-D36644707017}" name="Prestador" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{8A8AFA2B-D933-42D6-8F99-0EFE468F7729}" name="Fecha turno" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{7A644322-0847-4DF6-B2AA-BD3645BC40AA}" name="Fecha realización" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{404BB9DD-D07B-41FE-8D4B-8E476016E48E}" name="Resultado recibido (Sí/No)" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{8442E3CF-AA1A-423D-B00C-803F2F06C10B}" name="Fecha revisión médica" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{7597CA2D-54FC-4C2E-A1ED-24794DC93DAD}" name="Observaciones" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{BCC16971-5E1F-4801-81A8-354BB846221B}" name="Dias de Demora" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{48377B2A-C8AB-4075-A29A-A504CD024988}" name="Afiliado" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{FD0798EF-A11B-4C36-990B-871354CA5378}" name="DNI" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{FB341455-6534-4F40-A9B7-3851902BD371}" name="Estudio solicitado" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{2717F401-A0B9-4F33-8834-D45B603910EB}" name="Fecha solicitud" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{C94858FC-A376-4E19-928A-D36644707017}" name="Prestador" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{8A8AFA2B-D933-42D6-8F99-0EFE468F7729}" name="Fecha turno" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{7A644322-0847-4DF6-B2AA-BD3645BC40AA}" name="Fecha realización" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{404BB9DD-D07B-41FE-8D4B-8E476016E48E}" name="Resultado recibido (Sí/No)" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{8442E3CF-AA1A-423D-B00C-803F2F06C10B}" name="Fecha revisión médica" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{7597CA2D-54FC-4C2E-A1ED-24794DC93DAD}" name="Observaciones" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{BCC16971-5E1F-4801-81A8-354BB846221B}" name="Dias de Demora" dataDxfId="5">
       <calculatedColumnFormula>IF(D2="", 0, IF(G2&lt;&gt;"", G2-D2, TODAY()-D2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{A33CE862-3007-4162-B741-7D960E0BD2E7}" name="Turno Cancelado (Si/No)" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{5EBBC946-E3FF-45DD-91A2-8063369DD8CD}" name="Estado Automático" dataDxfId="0">
+    <tableColumn id="12" xr3:uid="{A33CE862-3007-4162-B741-7D960E0BD2E7}" name="Turno Cancelado (Si/No)" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{5EBBC946-E3FF-45DD-91A2-8063369DD8CD}" name="Estado Automático" dataDxfId="3">
       <calculatedColumnFormula>IF(L2="Si","⚫ Turno Cancelado",
    IF(G2&lt;&gt;"","🟢 Realizado",
       IF(TODAY()-D2&gt;10,"🔴 Pendiente",
@@ -929,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="22" style="14" customWidth="1"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="5">
         <v>46134</v>
@@ -1052,10 +1052,10 @@
       <c r="J3" s="9"/>
       <c r="K3" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M3" s="17" t="str">
         <f ca="1">IF(L3="Si","⚫ Turno Cancelado",
@@ -1065,7 +1065,7 @@
       )
    )
 )</f>
-        <v>🟠 Pendiente</v>
+        <v>⚫ Turno Cancelado</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -1087,10 +1087,10 @@
       <c r="J4" s="10"/>
       <c r="K4" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M4" s="17" t="str">
         <f ca="1">IF(L4="Si","⚫ Turno Cancelado",
@@ -1100,7 +1100,7 @@
       )
    )
 )</f>
-        <v>🔴 Pendiente</v>
+        <v>⚫ Turno Cancelado</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1122,7 +1122,7 @@
         <v>46042</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="23">
         <v>46042</v>
@@ -1149,22 +1149,48 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="6">
+        <f ca="1">IF(D6="", 0, IF(G6&lt;&gt;"", G6-D6, TODAY()-D6))</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="17" t="str">
+        <f ca="1">IF(L6="Si","⚫ Turno Cancelado",
+   IF(G6&lt;&gt;"","🟢 Realizado",
+      IF(TODAY()-D6&gt;10,"🔴 Pendiente",
+         "🟠 Pendiente"
+      )
+   )
+)</f>
+        <v>🔴 Pendiente</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L1 M1:M1048576">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="🟠">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="🟠">
       <formula>NOT(ISERROR(SEARCH("🟠",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="🔴">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="🔴">
       <formula>NOT(ISERROR(SEARCH("🔴",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="🟢">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="🟢">
       <formula>NOT(ISERROR(SEARCH("🟢",L1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576 H2:H1048576" xr:uid="{A25EE01D-F003-4F95-8E37-E6B02AB85919}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576 L2:L1048576" xr:uid="{A25EE01D-F003-4F95-8E37-E6B02AB85919}">
       <formula1>"Si,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/CIRCUITO ISSUNNE/Planilla_Seguimiento_UPCM_ISSUNNE.xlsx
+++ b/Excel/CIRCUITO ISSUNNE/Planilla_Seguimiento_UPCM_ISSUNNE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hernán\Desktop\Administracion HernanMayol\Python_ISSUNNE\Excel\CIRCUITO ISSUNNE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8F17B9-3785-4CC7-879C-FBFE2BE2681B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD86A68-1728-41FD-9D00-6E8D9B87E37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,27 +240,6 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -599,6 +578,27 @@
         </top>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -613,24 +613,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{327A5397-3B0C-43C9-85BE-3CBA3FCDD768}" name="Tabla1" displayName="Tabla1" ref="A1:M6" totalsRowShown="0" tableBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{327A5397-3B0C-43C9-85BE-3CBA3FCDD768}" name="Tabla1" displayName="Tabla1" ref="A1:M6" totalsRowShown="0" tableBorderDxfId="13">
   <autoFilter ref="A1:M6" xr:uid="{327A5397-3B0C-43C9-85BE-3CBA3FCDD768}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{48377B2A-C8AB-4075-A29A-A504CD024988}" name="Afiliado" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{FD0798EF-A11B-4C36-990B-871354CA5378}" name="DNI" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{FB341455-6534-4F40-A9B7-3851902BD371}" name="Estudio solicitado" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{2717F401-A0B9-4F33-8834-D45B603910EB}" name="Fecha solicitud" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{C94858FC-A376-4E19-928A-D36644707017}" name="Prestador" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{8A8AFA2B-D933-42D6-8F99-0EFE468F7729}" name="Fecha turno" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{7A644322-0847-4DF6-B2AA-BD3645BC40AA}" name="Fecha realización" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{404BB9DD-D07B-41FE-8D4B-8E476016E48E}" name="Resultado recibido (Sí/No)" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{8442E3CF-AA1A-423D-B00C-803F2F06C10B}" name="Fecha revisión médica" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{7597CA2D-54FC-4C2E-A1ED-24794DC93DAD}" name="Observaciones" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{BCC16971-5E1F-4801-81A8-354BB846221B}" name="Dias de Demora" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{48377B2A-C8AB-4075-A29A-A504CD024988}" name="Afiliado" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{FD0798EF-A11B-4C36-990B-871354CA5378}" name="DNI" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{FB341455-6534-4F40-A9B7-3851902BD371}" name="Estudio solicitado" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{2717F401-A0B9-4F33-8834-D45B603910EB}" name="Fecha solicitud" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{C94858FC-A376-4E19-928A-D36644707017}" name="Prestador" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{8A8AFA2B-D933-42D6-8F99-0EFE468F7729}" name="Fecha turno" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{7A644322-0847-4DF6-B2AA-BD3645BC40AA}" name="Fecha realización" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{404BB9DD-D07B-41FE-8D4B-8E476016E48E}" name="Resultado recibido (Sí/No)" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{8442E3CF-AA1A-423D-B00C-803F2F06C10B}" name="Fecha revisión médica" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{7597CA2D-54FC-4C2E-A1ED-24794DC93DAD}" name="Observaciones" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{BCC16971-5E1F-4801-81A8-354BB846221B}" name="Dias de Demora" dataDxfId="2">
       <calculatedColumnFormula>IF(D2="", 0, IF(G2&lt;&gt;"", G2-D2, TODAY()-D2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{A33CE862-3007-4162-B741-7D960E0BD2E7}" name="Turno Cancelado (Si/No)" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{5EBBC946-E3FF-45DD-91A2-8063369DD8CD}" name="Estado Automático" dataDxfId="3">
+    <tableColumn id="12" xr3:uid="{A33CE862-3007-4162-B741-7D960E0BD2E7}" name="Turno Cancelado (Si/No)" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{5EBBC946-E3FF-45DD-91A2-8063369DD8CD}" name="Estado Automático" dataDxfId="0">
       <calculatedColumnFormula>IF(L2="Si","⚫ Turno Cancelado",
    IF(G2&lt;&gt;"","🟢 Realizado",
       IF(TODAY()-D2&gt;10,"🔴 Pendiente",
@@ -1052,7 +1052,7 @@
       <c r="J3" s="9"/>
       <c r="K3" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L3" s="14" t="s">
         <v>15</v>
@@ -1087,7 +1087,7 @@
       <c r="J4" s="10"/>
       <c r="K4" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L4" s="14" t="s">
         <v>15</v>
@@ -1135,7 +1135,7 @@
         <v>3</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M5" s="17" t="str">
         <f ca="1">IF(L5="Si","⚫ Turno Cancelado",
@@ -1145,7 +1145,7 @@
       )
    )
 )</f>
-        <v>⚫ Turno Cancelado</v>
+        <v>🟢 Realizado</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -1179,13 +1179,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="L1 M1:M1048576">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="🟠">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="🟠">
       <formula>NOT(ISERROR(SEARCH("🟠",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="🔴">
+    <cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="🔴">
       <formula>NOT(ISERROR(SEARCH("🔴",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="🟢">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="🟢">
       <formula>NOT(ISERROR(SEARCH("🟢",L1)))</formula>
     </cfRule>
   </conditionalFormatting>
